--- a/artfynd/A 14348-2025 artfynd.xlsx
+++ b/artfynd/A 14348-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6871477</v>
+        <v>15561444</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,30 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>100857</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Robust tickgnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Dorcatoma robusta</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Strand, 1938</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brattåkersberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>719841.2472752542</v>
+        <v>719583</v>
       </c>
       <c r="R2" t="n">
-        <v>7135955.785306906</v>
+        <v>7135723</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -741,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-07-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-07-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,6 +761,11 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>fnösticka på björk</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -780,6 +779,299 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>15561477</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4872</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>101675</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Aspvedgnagare</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ptilinus fuscus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Geoffroy, 1785)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Brattåkersberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>719907</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7135906</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2013-07-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2013-07-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>död asp</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>6871476</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brattåkersberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>719891</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7135928</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2013-07-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2013-07-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6871477</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brattåkersberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>719841</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7135956</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2013-07-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2013-07-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14348-2025 artfynd.xlsx
+++ b/artfynd/A 14348-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15561444</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15561477</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6871476</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,8 +1092,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6871477</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>